--- a/feat/modeles-logiques-ror/ig/StructureDefinition-ror-entite-geographique.xlsx
+++ b/feat/modeles-logiques-ror/ig/StructureDefinition-ror-entite-geographique.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:04:08+00:00</t>
+    <t>2026-06-01T10:05:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feat/modeles-logiques-ror/ig/StructureDefinition-ror-entite-geographique.xlsx
+++ b/feat/modeles-logiques-ror/ig/StructureDefinition-ror-entite-geographique.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:05:41+00:00</t>
+    <t>2026-06-01T10:07:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feat/modeles-logiques-ror/ig/StructureDefinition-ror-entite-geographique.xlsx
+++ b/feat/modeles-logiques-ror/ig/StructureDefinition-ror-entite-geographique.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:07:23+00:00</t>
+    <t>2026-06-01T10:10:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feat/modeles-logiques-ror/ig/StructureDefinition-ror-entite-geographique.xlsx
+++ b/feat/modeles-logiques-ror/ig/StructureDefinition-ror-entite-geographique.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:10:00+00:00</t>
+    <t>2026-06-01T10:10:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
